--- a/www/download/IND.abstract_labour.emp.s.mv.rpA2.xlsx
+++ b/www/download/IND.abstract_labour.emp.s.mv.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>34921.542</t>
+          <t>34921542202.774</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35487.847</t>
+          <t>35487847293.0408</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36387.51</t>
+          <t>36387509597.4101</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37748.205</t>
+          <t>37748205156.6388</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>39036.659</t>
+          <t>39036659295.219</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>40671.009</t>
+          <t>40671008860.1504</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>41294.343</t>
+          <t>41294343285.8803</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43239.813</t>
+          <t>43239813139.7708</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>44631.223</t>
+          <t>44631222711.9125</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>45772.386</t>
+          <t>45772386083.1013</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>47142.48</t>
+          <t>47142479527.4827</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>48286.439</t>
+          <t>48286439359.5819</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>49605.096</t>
+          <t>49605095695.2532</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>53702.135</t>
+          <t>53702134649.4427</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>56603.347</t>
+          <t>56603346905.8065</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15996.993</t>
+          <t>15996993430.7709</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16347.693</t>
+          <t>16347693097.2018</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16748.891</t>
+          <t>16748891258.4175</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17074.374</t>
+          <t>17074373807.5073</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>17523.223</t>
+          <t>17523223052.3742</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17919.183</t>
+          <t>17919183086.1202</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>18277.412</t>
+          <t>18277411775.6058</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18394.352</t>
+          <t>18394352146.0095</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18493.258</t>
+          <t>18493258441.242</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>19500.412</t>
+          <t>19500411893.2471</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>19461.605</t>
+          <t>19461604745.4645</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>19479.733</t>
+          <t>19479733130.4129</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>19705.206</t>
+          <t>19705205518.398</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20300.233</t>
+          <t>20300232745.8802</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>19604.078</t>
+          <t>19604077718.6217</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13637.055</t>
+          <t>13637054501.4147</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13879.478</t>
+          <t>13879477982.2342</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14258.067</t>
+          <t>14258067119.5708</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14647.151</t>
+          <t>14647150669.1955</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>15045.755</t>
+          <t>15045754772.4849</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15740.278</t>
+          <t>15740278418.849</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16146.021</t>
+          <t>16146021096.6998</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16192.208</t>
+          <t>16192208313.4864</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>16320.43</t>
+          <t>16320430443.5021</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>16906.052</t>
+          <t>16906051819.7242</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17232.559</t>
+          <t>17232558974.4055</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>17644.971</t>
+          <t>17644971338.0964</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>18012.982</t>
+          <t>18012981864.2733</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>19049.861</t>
+          <t>19049861102.2779</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>19064.151</t>
+          <t>19064151101.005</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10155.328</t>
+          <t>10155327990.7334</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10478.29</t>
+          <t>10478289632.5577</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9905.52</t>
+          <t>9905520133.85062</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9106.412</t>
+          <t>9106412403.37489</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8985.988</t>
+          <t>8985987793.29995</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8584.441</t>
+          <t>8584440600.37619</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8618.425</t>
+          <t>8618424726.57872</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8643.082</t>
+          <t>8643082443.24503</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9201.438</t>
+          <t>9201438478.33207</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9949.93</t>
+          <t>9949929641.93705</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10289.425</t>
+          <t>10289424546.2409</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10776.281</t>
+          <t>10776281108.2906</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>11261.029</t>
+          <t>11261029457.477</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>11780.567</t>
+          <t>11780566531.5442</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>11940.216</t>
+          <t>11940216496.7314</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>288869.931</t>
+          <t>288869930534.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>287777.774</t>
+          <t>287777774035.241</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>299007.321</t>
+          <t>299007320950.987</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>303084.755</t>
+          <t>303084754942.59</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>318760.528</t>
+          <t>318760528292.589</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>336610.448</t>
+          <t>336610448008.449</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>346157.491</t>
+          <t>346157491259.901</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>363771.389</t>
+          <t>363771389008.994</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>375773.577</t>
+          <t>375773577325.512</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>398086.591</t>
+          <t>398086591459.614</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>413117.655</t>
+          <t>413117655388.456</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>437040.861</t>
+          <t>437040860962.247</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>458769.288</t>
+          <t>458769287749.135</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>477915.159</t>
+          <t>477915158991.936</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>492941.437</t>
+          <t>492941437153.661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>75275.99</t>
+          <t>75275989507.9021</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>76955.707</t>
+          <t>76955706645.5813</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78472.032</t>
+          <t>78472031995.5129</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80719.606</t>
+          <t>80719605529.9711</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>82935.746</t>
+          <t>82935746212.5312</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>85433.54</t>
+          <t>85433540457.0861</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>86553.144</t>
+          <t>86553144191.8719</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>87702.863</t>
+          <t>87702862860.8171</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>89702.936</t>
+          <t>89702936078.4577</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>92400.986</t>
+          <t>92400985513.5217</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>94112.482</t>
+          <t>94112481782.3699</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>96269.106</t>
+          <t>96269106264.6511</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>99027.352</t>
+          <t>99027351562.8589</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>101358.251</t>
+          <t>101358250574.724</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>97281.975</t>
+          <t>97281975327.6295</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1935111.915</t>
+          <t>1935111914772.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1994912.129</t>
+          <t>1994912128922.21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2033898.13</t>
+          <t>2033898129511.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2048516.75</t>
+          <t>2048516750225.77</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2062207.424</t>
+          <t>2062207423711.25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2129279.722</t>
+          <t>2129279722120.48</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2315952.603</t>
+          <t>2315952603232.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2458222.34</t>
+          <t>2458222339924</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2562735.929</t>
+          <t>2562735928716.01</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2634853.25</t>
+          <t>2634853250152.85</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2707650.739</t>
+          <t>2707650739284.36</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2715179.174</t>
+          <t>2715179174118.36</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2751911.249</t>
+          <t>2751911248976.79</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2869946.09</t>
+          <t>2869946090337.57</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2927750.525</t>
+          <t>2927750524810.68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1733.592</t>
+          <t>1733591898.49232</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1763.932</t>
+          <t>1763931677.63058</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1737.575</t>
+          <t>1737574518.05486</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1710.98</t>
+          <t>1710980184.32264</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1764.958</t>
+          <t>1764957669.11074</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1830.371</t>
+          <t>1830370677.43478</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1928.193</t>
+          <t>1928192941.96541</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1974.484</t>
+          <t>1974484134.21067</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2034.91</t>
+          <t>2034909705.46725</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2073.553</t>
+          <t>2073552748.64398</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2118.144</t>
+          <t>2118144007.32021</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2213.071</t>
+          <t>2213071217.34193</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2365.916</t>
+          <t>2365916028.23726</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2457.55</t>
+          <t>2457550481.15767</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2439.234</t>
+          <t>2439233563.59828</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>28977.639</t>
+          <t>28977638704.0643</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29202.441</t>
+          <t>29202441405.3505</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29330.381</t>
+          <t>29330381458.7203</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28993.445</t>
+          <t>28993445455.3329</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>28678.09</t>
+          <t>28678090370.3233</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>28822.208</t>
+          <t>28822208104.4962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27839.229</t>
+          <t>27839228706.8984</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>27903.941</t>
+          <t>27903941090.9461</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27748.723</t>
+          <t>27748723071.1546</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>28260.567</t>
+          <t>28260567103.1742</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>28960.377</t>
+          <t>28960377379.6088</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>29548.5</t>
+          <t>29548499880.1146</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>30151.238</t>
+          <t>30151237915.3542</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>31370.804</t>
+          <t>31370803716.0985</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>30875.357</t>
+          <t>30875357075.8705</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>177425.927</t>
+          <t>177425926629.721</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>174515.976</t>
+          <t>174515975957.612</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>173121.02</t>
+          <t>173121019743.326</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>178940.299</t>
+          <t>178940299119.153</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>179355.141</t>
+          <t>179355141146.38</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>179683.133</t>
+          <t>179683133029.321</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>179878.685</t>
+          <t>179878685361.945</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>178820.342</t>
+          <t>178820341641.315</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>180525.117</t>
+          <t>180525117431.092</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>184479.397</t>
+          <t>184479397188.585</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>180910.643</t>
+          <t>180910643316.415</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>180004.37</t>
+          <t>180004369849.266</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>183558.761</t>
+          <t>183558761423.858</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>188436.315</t>
+          <t>188436315064.82</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>188684.981</t>
+          <t>188684981102.741</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12003.546</t>
+          <t>12003545612.3177</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12204.351</t>
+          <t>12204351241.9802</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12701.598</t>
+          <t>12701597971.6838</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13123.959</t>
+          <t>13123958942.8509</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13473.403</t>
+          <t>13473402915.2382</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13755.874</t>
+          <t>13755873796.7203</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14069.67</t>
+          <t>14069670437.3369</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14211.21</t>
+          <t>14211209820.5613</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14303.534</t>
+          <t>14303534144.7504</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14348.82</t>
+          <t>14348819514.0726</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14629.069</t>
+          <t>14629069009.9054</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>15142.889</t>
+          <t>15142888638.3021</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14579.112</t>
+          <t>14579112377.7942</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>15277.975</t>
+          <t>15277974966.177</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14679.774</t>
+          <t>14679773639.505</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>55245.89</t>
+          <t>55245890222.7015</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>58600.114</t>
+          <t>58600114490.6944</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>61795.309</t>
+          <t>61795309185.4857</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>66213.141</t>
+          <t>66213141350.1077</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>70805.803</t>
+          <t>70805802704.6476</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>76589.31</t>
+          <t>76589310236.7262</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>80724.624</t>
+          <t>80724624359.0227</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>83380.442</t>
+          <t>83380442275.8595</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>86188.096</t>
+          <t>86188096127.9358</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>90283.999</t>
+          <t>90283999399.2017</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>95626.437</t>
+          <t>95626436691.3846</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>99448.305</t>
+          <t>99448304629.2088</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>102519.854</t>
+          <t>102519853637.06</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>103891.995</t>
+          <t>103891995014.19</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>100755.42</t>
+          <t>100755420179.331</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4416.977</t>
+          <t>4416977333.32594</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4320.92</t>
+          <t>4320920254.19147</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4249.814</t>
+          <t>4249814217.59962</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4093.255</t>
+          <t>4093255491.99862</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3877.98</t>
+          <t>3877979896.69587</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3839.125</t>
+          <t>3839125148.51987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3926.292</t>
+          <t>3926291804.37937</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4018.51</t>
+          <t>4018509900.19315</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4038.525</t>
+          <t>4038525010.52873</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4123.504</t>
+          <t>4123504016.55552</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4351.841</t>
+          <t>4351841048.32023</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4574.906</t>
+          <t>4574905595.37915</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4600.482</t>
+          <t>4600482260.79432</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4609.026</t>
+          <t>4609025729.29185</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4147.631</t>
+          <t>4147631232.07811</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11824.542</t>
+          <t>11824541807.3975</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12121.734</t>
+          <t>12121734176.2485</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12606.039</t>
+          <t>12606039268.0658</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>12740.196</t>
+          <t>12740196312.8464</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13128.883</t>
+          <t>13128883274.0571</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13330.699</t>
+          <t>13330699204.1195</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13554.064</t>
+          <t>13554064025.7082</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13758.047</t>
+          <t>13758047072.7066</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13867.405</t>
+          <t>13867404756.6522</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14111.292</t>
+          <t>14111291877.9093</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>14315.268</t>
+          <t>14315267889.3</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>14615.712</t>
+          <t>14615711647.4503</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>15079.85</t>
+          <t>15079850253.078</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>15356.713</t>
+          <t>15356712511.8207</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>15075.274</t>
+          <t>15075273604.8837</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>97961.356</t>
+          <t>97961355873.6062</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>99909.85</t>
+          <t>99909849648.4536</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>101939.931</t>
+          <t>101939931126.307</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>104670.826</t>
+          <t>104670826376.23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>109077.254</t>
+          <t>109077254112.299</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>111089.537</t>
+          <t>111089537272.252</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>113734.319</t>
+          <t>113734319298.647</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>112621.93</t>
+          <t>112621930279.084</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>112563.614</t>
+          <t>112563614231.382</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>115745.263</t>
+          <t>115745262988.782</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>118322.823</t>
+          <t>118322822607.877</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>119697.864</t>
+          <t>119697863823.2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>124462.336</t>
+          <t>124462336363.387</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>128017.232</t>
+          <t>128017231842.865</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>126775.037</t>
+          <t>126775036844.596</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>127800.297</t>
+          <t>127800296534.874</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>130190.111</t>
+          <t>130190110772.353</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>136909.287</t>
+          <t>136909286977.464</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>141433.172</t>
+          <t>141433172204.86</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>145890.258</t>
+          <t>145890258014.851</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>149888.606</t>
+          <t>149888606436.505</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>152728.69</t>
+          <t>152728690163.227</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>154913.707</t>
+          <t>154913707423.787</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>155619.001</t>
+          <t>155619000538.951</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>157476.428</t>
+          <t>157476427614.686</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>160949.123</t>
+          <t>160949123291.917</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>164092.928</t>
+          <t>164092927522.042</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>167696.641</t>
+          <t>167696640778.55</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>168011.023</t>
+          <t>168011022791.349</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>168309.847</t>
+          <t>168309847487.683</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20247.651</t>
+          <t>20247651450.9689</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20228.327</t>
+          <t>20228327179.4065</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20222.331</t>
+          <t>20222331231.1796</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>21660.187</t>
+          <t>21660186542.1408</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22408.297</t>
+          <t>22408297149.9752</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22797.594</t>
+          <t>22797594446.935</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22932.337</t>
+          <t>22932336749.8021</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23921.205</t>
+          <t>23921204774.3118</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24398.391</t>
+          <t>24398391012.5713</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25948.645</t>
+          <t>25948644530.8615</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>26320.999</t>
+          <t>26320999014.8868</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>28570.287</t>
+          <t>28570287186.7604</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>28911.612</t>
+          <t>28911612239.6709</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>29131.576</t>
+          <t>29131575991.8069</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>29960.184</t>
+          <t>29960184202.0516</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22444.183</t>
+          <t>22444182956.0354</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22314.992</t>
+          <t>22314991757.9375</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22545.267</t>
+          <t>22545267395.4464</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23012.259</t>
+          <t>23012259456.8365</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>24662.471</t>
+          <t>24662470620.9413</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24534.273</t>
+          <t>24534273144.3499</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>23958.99</t>
+          <t>23958989755.2891</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24272.048</t>
+          <t>24272048351.9355</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>24585.459</t>
+          <t>24585459334.5948</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25008.976</t>
+          <t>25008975850.9127</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>25168.717</t>
+          <t>25168716556.0291</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>25470.079</t>
+          <t>25470078928.0567</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>25488.566</t>
+          <t>25488566472.8224</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>25226.384</t>
+          <t>25226384379.6945</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>24908.047</t>
+          <t>24908047093.4622</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>187267.528</t>
+          <t>187267527680.02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>200221.273</t>
+          <t>200221273269.595</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>204567.787</t>
+          <t>204567787249.281</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>218901.674</t>
+          <t>218901674304.276</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>250004.925</t>
+          <t>250004924777.352</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>248007.936</t>
+          <t>248007935690.35</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>250202.897</t>
+          <t>250202897413.361</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>262698.867</t>
+          <t>262698866996.519</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>269205.398</t>
+          <t>269205398370.14</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>284927.355</t>
+          <t>284927354627.82</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>243683.524</t>
+          <t>243683523617.007</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>238035.877</t>
+          <t>238035877153.66</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>244666.466</t>
+          <t>244666466014.792</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>252676.241</t>
+          <t>252676240774.211</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>260727.932</t>
+          <t>260727932430.966</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1436494.432</t>
+          <t>1436494432158.03</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1494850.421</t>
+          <t>1494850421126.58</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1528347.155</t>
+          <t>1528347154607.75</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1556117.707</t>
+          <t>1556117706716.62</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1563538.67</t>
+          <t>1563538669723.27</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1658148.762</t>
+          <t>1658148762435.4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1753697.301</t>
+          <t>1753697300542.69</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1768292.774</t>
+          <t>1768292773510</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1906849.19</t>
+          <t>1906849189786.21</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1975897.435</t>
+          <t>1975897434942.8</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025474.612</t>
+          <t>2025474611910.7</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2034829.156</t>
+          <t>2034829156088.68</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2007354.286</t>
+          <t>2007354286254.56</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2031796.436</t>
+          <t>2031796436223.74</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2052201.346</t>
+          <t>2052201346091.07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6881.716</t>
+          <t>6881715620.60314</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7412.791</t>
+          <t>7412791081.24025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7775.129</t>
+          <t>7775128644.71266</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>8489.872</t>
+          <t>8489871845.1403</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9097.337</t>
+          <t>9097337458.10121</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9532.529</t>
+          <t>9532529314.04689</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9886.358</t>
+          <t>9886357998.09175</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>10298.095</t>
+          <t>10298094684.6471</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>10706.563</t>
+          <t>10706562659.6657</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>11243.406</t>
+          <t>11243405574.0897</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>11984.252</t>
+          <t>11984252427.0932</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>12703.664</t>
+          <t>12703663928.6757</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>13328.12</t>
+          <t>13328120431.7444</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>13950.802</t>
+          <t>13950801878.7666</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>13153.331</t>
+          <t>13153331250.006</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>79853.776</t>
+          <t>79853775648.1248</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>82784.791</t>
+          <t>82784790912.4061</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84793.095</t>
+          <t>84793095066.4534</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>88652.102</t>
+          <t>88652101910.435</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>92100.437</t>
+          <t>92100437054.3101</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>95156.551</t>
+          <t>95156551170.7407</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>95382.128</t>
+          <t>95382128007.0405</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>97592.551</t>
+          <t>97592551325.7616</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>100775.955</t>
+          <t>100775955495.642</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>101845.661</t>
+          <t>101845661327.336</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>104909.201</t>
+          <t>104909200812.226</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>108330.182</t>
+          <t>108330182443.347</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>111525.602</t>
+          <t>111525601574.301</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>114614.994</t>
+          <t>114614993813.482</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>111955.464</t>
+          <t>111955464328.865</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>382726.006</t>
+          <t>382726006448.701</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>389284.549</t>
+          <t>389284549228.69</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>391676.126</t>
+          <t>391676125901.014</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>388633.926</t>
+          <t>388633925677.604</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>383923.988</t>
+          <t>383923988139.899</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>389925.328</t>
+          <t>389925327579.717</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>392107.376</t>
+          <t>392107376070.73</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>387820.54</t>
+          <t>387820539800.315</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>393525.192</t>
+          <t>393525191645.974</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>396059.821</t>
+          <t>396059820600.167</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>393133.472</t>
+          <t>393133471820.06</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>398136.071</t>
+          <t>398136071209.141</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>399710.537</t>
+          <t>399710537203.396</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>390385.671</t>
+          <t>390385670608.185</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>360330.389</t>
+          <t>360330389354.384</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>169950.946</t>
+          <t>169950946339.136</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>174452.798</t>
+          <t>174452797690.867</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>179697.995</t>
+          <t>179697995387.734</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>176225.212</t>
+          <t>176225212073.425</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>186735.091</t>
+          <t>186735090696.894</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>193998.6</t>
+          <t>193998600336.047</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>200914.405</t>
+          <t>200914405006.013</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>211800.944</t>
+          <t>211800943600.719</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>213849.484</t>
+          <t>213849483832.749</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>227383.105</t>
+          <t>227383105374.008</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>223891.037</t>
+          <t>223891037079.52</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>226097.377</t>
+          <t>226097377300.331</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>221519.585</t>
+          <t>221519585436.248</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>222871.237</t>
+          <t>222871236772.542</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>222200.137</t>
+          <t>222200137158.018</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8695.098</t>
+          <t>8695098406.1125</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8741.907</t>
+          <t>8741907182.64329</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8701.417</t>
+          <t>8701417461.47426</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8603.437</t>
+          <t>8603437037.49791</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8126.127</t>
+          <t>8126127358.50377</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8423.641</t>
+          <t>8423640783.39861</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8117.89</t>
+          <t>8117890061.3451</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8332.169</t>
+          <t>8332169289.88257</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8517.213</t>
+          <t>8517213440.40721</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8825.507</t>
+          <t>8825506560.57832</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9570.913</t>
+          <t>9570912962.89838</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9746.988</t>
+          <t>9746987638.10926</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10323.885</t>
+          <t>10323885224.0626</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10771.992</t>
+          <t>10771991781.5595</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10133.247</t>
+          <t>10133246949.737</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>893.335</t>
+          <t>893334854.728713</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>909.848</t>
+          <t>909848169.687026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>963.743</t>
+          <t>963743388.988674</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1030.716</t>
+          <t>1030715705.67243</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1124.677</t>
+          <t>1124676874.53457</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1192.307</t>
+          <t>1192307437.04167</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1243.634</t>
+          <t>1243633685.25711</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1283.601</t>
+          <t>1283601289.67021</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1186.413</t>
+          <t>1186413034.04949</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1452.303</t>
+          <t>1452303246.89539</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1528.898</t>
+          <t>1528897989.90964</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1523.711</t>
+          <t>1523711052.8137</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1650.293</t>
+          <t>1650292887.40952</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1881.937</t>
+          <t>1881936961.63328</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2021.125</t>
+          <t>2021124613.43463</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4955.29</t>
+          <t>4955290205.50733</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4928.919</t>
+          <t>4928919185.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4906.48</t>
+          <t>4906480403.8255</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4976.232</t>
+          <t>4976231650.63778</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4949.233</t>
+          <t>4949233196.02903</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4892.913</t>
+          <t>4892913378.48021</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4819.468</t>
+          <t>4819468486.28008</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4830.204</t>
+          <t>4830203595.65809</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4798.996</t>
+          <t>4798996250.89012</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5047.307</t>
+          <t>5047307425.34951</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5182.419</t>
+          <t>5182418661.15747</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5388.139</t>
+          <t>5388138898.48526</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5691.794</t>
+          <t>5691794313.12519</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5703.649</t>
+          <t>5703648611.93538</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5037.831</t>
+          <t>5037830737.60443</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>154583.669</t>
+          <t>154583669300.023</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>161180.832</t>
+          <t>161180831822.752</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>167909.414</t>
+          <t>167909413938.736</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>172344.227</t>
+          <t>172344226626.661</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>179376.556</t>
+          <t>179376556030.919</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>186593.304</t>
+          <t>186593304471.612</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>192980.837</t>
+          <t>192980837491.476</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>197569.399</t>
+          <t>197569399294.652</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>203263.298</t>
+          <t>203263298446.367</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>214846.205</t>
+          <t>214846205226.631</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>221493.104</t>
+          <t>221493104346.6</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>225132.869</t>
+          <t>225132868999.634</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>228546.245</t>
+          <t>228546245074.563</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>244818.484</t>
+          <t>244818484208.255</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>241454.898</t>
+          <t>241454898040.491</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>500.14</t>
+          <t>500139945.279738</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>504.716</t>
+          <t>504716047.729708</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>492.003</t>
+          <t>492002509.942257</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>484.152</t>
+          <t>484151608.15385</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>496.741</t>
+          <t>496741069.857772</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>506.03</t>
+          <t>506029598.512922</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>437.682</t>
+          <t>437681764.141144</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>519.526</t>
+          <t>519525928.548431</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>526.166</t>
+          <t>526165846.23679</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>566.399</t>
+          <t>566398748.282775</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>574.002</t>
+          <t>574002283.658738</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>591.352</t>
+          <t>591351801.430865</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>616.873</t>
+          <t>616873359.666589</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>648.027</t>
+          <t>648027223.101024</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>674.378</t>
+          <t>674377514.142872</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>28706.057</t>
+          <t>28706056860.4672</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>30014.926</t>
+          <t>30014926080.9492</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>31531.943</t>
+          <t>31531942749.9339</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>32300.925</t>
+          <t>32300925262.5815</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>35011.286</t>
+          <t>35011285682.7651</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>33181.118</t>
+          <t>33181117547.3098</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>33543.394</t>
+          <t>33543394275.4357</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>34458.932</t>
+          <t>34458932002.3842</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>35582.157</t>
+          <t>35582156837.1294</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>36344.668</t>
+          <t>36344668246.241</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>36855.395</t>
+          <t>36855394941.3833</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>37499.261</t>
+          <t>37499260574.7031</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>38667.313</t>
+          <t>38667313185.583</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>39647.293</t>
+          <t>39647293089.0944</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>39456.556</t>
+          <t>39456555865.8591</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>74042.234</t>
+          <t>74042234037.9819</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>75401.433</t>
+          <t>75401433194.3399</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>77771.291</t>
+          <t>77771290733.7853</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>79554.213</t>
+          <t>79554212879.0217</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>79299.952</t>
+          <t>79299951508.4066</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>76553.059</t>
+          <t>76553058923.776</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>73096.046</t>
+          <t>73096046434.3458</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>72086.913</t>
+          <t>72086912511.1222</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>73565.591</t>
+          <t>73565590846.4519</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>76731.214</t>
+          <t>76731214461.6207</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>79042.37</t>
+          <t>79042370120.1452</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>82515.682</t>
+          <t>82515682039.5835</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>86558.885</t>
+          <t>86558884664.5483</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>90237.821</t>
+          <t>90237821206.0098</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>91935.073</t>
+          <t>91935073217.9423</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13851.662</t>
+          <t>13851661614.0999</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13979.651</t>
+          <t>13979651356.3892</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13675.701</t>
+          <t>13675700786.6723</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13560.16</t>
+          <t>13560159983.4232</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14095.184</t>
+          <t>14095184327.0342</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14502.466</t>
+          <t>14502466222.0144</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>14826.633</t>
+          <t>14826632821.8365</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>15079.553</t>
+          <t>15079552906.3783</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>15422.16</t>
+          <t>15422159859.6662</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>16250.661</t>
+          <t>16250660533.6917</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16456.603</t>
+          <t>16456603303.2346</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>17432.925</t>
+          <t>17432924508.0096</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>17811.384</t>
+          <t>17811384467.3727</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>18235.655</t>
+          <t>18235655049.9905</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>18188.287</t>
+          <t>18188287488.9147</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25489.58</t>
+          <t>25489580305.8645</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26240.918</t>
+          <t>26240917715.1982</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24332.705</t>
+          <t>24332705391.4853</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>23435.489</t>
+          <t>23435489378.3416</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>27856.945</t>
+          <t>27856945390.8238</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>27879.4</t>
+          <t>27879399785.4423</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>27738.585</t>
+          <t>27738585129.9635</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>26513.72</t>
+          <t>26513719793.2214</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27063.509</t>
+          <t>27063509234.9383</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>28117.278</t>
+          <t>28117277894.7499</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>28187.094</t>
+          <t>28187094451.8946</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>28889.656</t>
+          <t>28889656314.7991</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>29575.965</t>
+          <t>29575965103.5518</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>30340.726</t>
+          <t>30340725507.3137</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>30880.209</t>
+          <t>30880208553.2599</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>407981.343</t>
+          <t>407981343211.84</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>404310.555</t>
+          <t>404310555315.057</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>398917.197</t>
+          <t>398917197154.39</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>388216.32</t>
+          <t>388216320162.657</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>392152.674</t>
+          <t>392152673675.451</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>398470.589</t>
+          <t>398470589158.602</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>406355.086</t>
+          <t>406355085989.24</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>413196.211</t>
+          <t>413196211486.252</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>420442.489</t>
+          <t>420442489159.873</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>427261.51</t>
+          <t>427261509682.552</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>430684.964</t>
+          <t>430684964398.331</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>433798.123</t>
+          <t>433798122683.574</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>439522.086</t>
+          <t>439522086089.629</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>442184.243</t>
+          <t>442184243315.652</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>431547.84</t>
+          <t>431547839622.154</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>11320.454</t>
+          <t>11320454203.5128</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11271.216</t>
+          <t>11271216107.0257</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11177.305</t>
+          <t>11177305288.8565</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>11005.966</t>
+          <t>11005965517.2128</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10752.055</t>
+          <t>10752055239.4196</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>10682.719</t>
+          <t>10682718505.6747</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10644.762</t>
+          <t>10644761712.7191</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10456.933</t>
+          <t>10456933120.1258</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>10322.258</t>
+          <t>10322257899.1048</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>10738.806</t>
+          <t>10738805749.0761</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>11297.809</t>
+          <t>11297809271.4509</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>11518.391</t>
+          <t>11518390990.4777</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>11946.17</t>
+          <t>11946169546.5852</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>12430.009</t>
+          <t>12430008875.2755</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>12427.229</t>
+          <t>12427228613.0919</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4594.722</t>
+          <t>4594721821.3504</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4528.753</t>
+          <t>4528752824.27117</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4461.456</t>
+          <t>4461456127.21485</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4460.019</t>
+          <t>4460018977.9466</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4593.169</t>
+          <t>4593168768.61058</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4728.338</t>
+          <t>4728338371.50675</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4578.486</t>
+          <t>4578485528.71043</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4751.067</t>
+          <t>4751066780.90985</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4935.3</t>
+          <t>4935300226.74854</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5028.209</t>
+          <t>5028208933.96904</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5074.165</t>
+          <t>5074164783.81851</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5263.69</t>
+          <t>5263689585.15788</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>5462.64</t>
+          <t>5462639764.35569</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>5725.683</t>
+          <t>5725683054.83116</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>5727.967</t>
+          <t>5727967016.72911</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>19173.857</t>
+          <t>19173856687.3595</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19289.19</t>
+          <t>19289189986.4676</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19291.93</t>
+          <t>19291930014.1386</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>19727.817</t>
+          <t>19727816986.4466</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20511.398</t>
+          <t>20511397920.9232</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>21904.347</t>
+          <t>21904347314.0347</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>22419.609</t>
+          <t>22419609025.3683</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22227.447</t>
+          <t>22227446997.8828</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>22088.665</t>
+          <t>22088665436.6535</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>22558.488</t>
+          <t>22558487764.7921</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>22901.464</t>
+          <t>22901463553.4399</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>23591.136</t>
+          <t>23591135996.2358</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>24631.092</t>
+          <t>24631092284.9059</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>25077.237</t>
+          <t>25077237427.3797</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>24356.421</t>
+          <t>24356420588.1456</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>65772.47</t>
+          <t>65772470036.1448</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>69561.861</t>
+          <t>69561861496.2725</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>71985.161</t>
+          <t>71985160813.4388</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70427.411</t>
+          <t>70427410996.0424</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>71880.553</t>
+          <t>71880552548.7504</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>72262.497</t>
+          <t>72262496807.5121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>72832.756</t>
+          <t>72832755555.4991</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>74602.263</t>
+          <t>74602262782.8059</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>76465.995</t>
+          <t>76465995304.7952</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>76002.452</t>
+          <t>76002451581.0659</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>81290.776</t>
+          <t>81290776423.569</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>80528.338</t>
+          <t>80528338425.8053</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>81037.741</t>
+          <t>81037741427.6947</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>83585.565</t>
+          <t>83585565270.4043</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>84577.099</t>
+          <t>84577098611.746</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>53396.929</t>
+          <t>53396929489.7536</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>53732.744</t>
+          <t>53732743596.9577</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>55337.429</t>
+          <t>55337428747.7906</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>55784.087</t>
+          <t>55784086785.8542</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>57094.065</t>
+          <t>57094065338.6156</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>58959.034</t>
+          <t>58959034100.1144</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>56663.632</t>
+          <t>56663632287.825</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>58071.56</t>
+          <t>58071559892.2699</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>59752.551</t>
+          <t>59752550901.2505</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>62388.945</t>
+          <t>62388944707.5275</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>64695.241</t>
+          <t>64695240652.8086</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>67147.139</t>
+          <t>67147139041.5758</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>69744.607</t>
+          <t>69744606563.2744</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>72611.188</t>
+          <t>72611188406.8283</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>72756.727</t>
+          <t>72756727225.9467</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>795645.348</t>
+          <t>795645347744.743</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>814367.288</t>
+          <t>814367288232.58</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>836330.654</t>
+          <t>836330653709.28</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>863588.546</t>
+          <t>863588546011.44</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>881321.118</t>
+          <t>881321117528.403</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>904568.794</t>
+          <t>904568794010.581</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>895764.201</t>
+          <t>895764201085.918</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>885470.276</t>
+          <t>885470275602.398</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>887336.21</t>
+          <t>887336210092.949</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>905823.592</t>
+          <t>905823592446.395</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>918743.492</t>
+          <t>918743492282.992</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>943816.155</t>
+          <t>943816154649.907</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>958507.06</t>
+          <t>958507059808.422</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>955767.132</t>
+          <t>955767131948.07</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>920894.631</t>
+          <t>920894631140.938</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3320242.898</t>
+          <t>3320242898424.88</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3477304.47</t>
+          <t>3477304469818.57</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3573433.985</t>
+          <t>3573433984902.78</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3610298.842</t>
+          <t>3610298841574.19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3683118.334</t>
+          <t>3683118333943.08</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3877385.371</t>
+          <t>3877385370585.73</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4099988.703</t>
+          <t>4099988702527.05</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4217746.235</t>
+          <t>4217746234901.34</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4488359.841</t>
+          <t>4488359841384.35</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>4804773.001</t>
+          <t>4804773000783.46</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>4941221.109</t>
+          <t>4941221109196.17</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5128321.261</t>
+          <t>5128321260566.66</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>5346255.758</t>
+          <t>5346255757578.41</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>5650709.423</t>
+          <t>5650709423311.55</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>5842563.994</t>
+          <t>5842563994054.34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10187069.843</t>
+          <t>10187069843008</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10526487.518</t>
+          <t>10526487517611.5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10763913.125</t>
+          <t>10763913124639.8</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10904308.024</t>
+          <t>10904308023843</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>11114778.375</t>
+          <t>11114778375256.2</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>11557854.987</t>
+          <t>11557854986576.5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>12096516.402</t>
+          <t>12096516402073.1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>12421661.693</t>
+          <t>12421661692694.7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>12997272.164</t>
+          <t>12997272163552.3</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>13579443.376</t>
+          <t>13579443375836.5</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>13858556.302</t>
+          <t>13858556302351.8</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>14148892.617</t>
+          <t>14148892617089.6</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>14462360.959</t>
+          <t>14462360958833</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>14982510.333</t>
+          <t>14982510332742.5</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15186998.626</t>
+          <t>15186998626007.7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.emp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
